--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0082.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0082.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Severely Mutated Sample</t>
+          <t>Mẫu Vật Chất Đột Biến Nặng</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Strongest Sound</t>
+          <t>Âm Thanh Hùng Mạnh Nhất</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Red Needle</t>
+          <t>Kim Đỏ</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Tacet Field Survival Guide</t>
+          <t>Hướng Dẫn Sinh Tồn Trong Tổ Tacet</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Power Hammer</t>
+          <t>Búa Năng Lượng</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Unidentified Plant</t>
+          <t>Thực Vật Không Xác Định</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Hidden Blade</t>
+          <t>Lưỡi Kiếm Ẩn</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Severely Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Nặng</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Modernized Device</t>
+          <t>Thiết Bị Hiện Đại Hóa</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Tracking Goggles</t>
+          <t>Kính Theo Dõi</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Khát Khao Hủy Diệt</t>
+          <t>Khát Vọng Hủy Diệt</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Cái Giá của Sự Phá Hủy</t>
+          <t>Giá Trị của Sự Hủy Diệt</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1484,7 +1484,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Crude Nameplate</t>
+          <t>Bảng Tên Thô</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1554,7 +1554,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>Nameplate</t>
+          <t>Bảng tên</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1624,7 +1624,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Bảng Tên của Kẻ Vô Danh</t>
+          <t>Bảng tên của một Kẻ Vô Danh</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1694,7 +1694,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Inferior Spring</t>
+          <t>Mùa Xuân Thấp Kém</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1764,7 +1764,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Mùa Xuân</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Elastic Spring</t>
+          <t>Lò Xo Đàn Hồi</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1904,7 +1904,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Exquisite Tacetite Bloom</t>
+          <t>Đóa Tacetite Tuyệt Mỹ</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1974,7 +1974,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Tacetite Bloom</t>
+          <t>Nở Hoa Tacetite</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2044,7 +2044,7 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>Brilliant Tacetite Bloom</t>
+          <t>Đóa Tacetite Rực Rỡ</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>La bàn</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cao Nguyên</t>
+          <t>Giấc Mộng Cao Nguyên</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Rapid Grapple</t>
+          <t>Túm Nhanh</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Guardian's Proof</t>
+          <t>Chứng Cứ Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Guardian's Promise</t>
+          <t>Lời Hứa Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Guardian's Pledge</t>
+          <t>Lời Thề Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Dangerous Data</t>
+          <t>Dữ liệu nguy hiểm</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Chìa Khóa Bình Yên</t>
+          <t>Chìa Khóa Thanh Bình</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Chìa Khóa Run Rẩy</t>
+          <t>Chìa Khóa Rung Chấn</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2884,7 +2884,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Companion's Aid</t>
+          <t>Sự Giúp Đỡ Của Đồng Hành</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Companion's Aid</t>
+          <t>Sự Giúp Đỡ Của Đồng Hành</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Companion's Aid</t>
+          <t>Sự Giúp Đỡ Của Đồng Hành</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Companion's Aid</t>
+          <t>Sự Giúp Đỡ Của Đồng Hành</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Companion's Aid</t>
+          <t>Sự Giúp Đỡ Của Đồng Hành</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Grapple 1</t>
+          <t>Móc 1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Tăng Tốc Độ Tấn Công sau khi sử dụng Móc Treo</t>
+          <t>Tốc độ Tấn Công tăng sau khi dùng Móc Câu</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Grapple 3</t>
+          <t>Móc 3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Destroyer's Promise</t>
+          <t>Lời Hứa Của Kẻ Hủy Diệt</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Critical Hit 3</t>
+          <t>Bạo Kích 3</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Old Revolver</t>
+          <t>Khẩu Súng Lục Cũ</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Boxing Gloves</t>
+          <t>Găng Tay Quyền Anh</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Critical Hit 7</t>
+          <t>Bạo Kích 7</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Mobile Combat Boots</t>
+          <t>Giày Chiến Đấu Cơ Động</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Compound Spring</t>
+          <t>Lò Xo Ghép</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Dream Recipe</t>
+          <t>Công Thức Giấc Mơ</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Grapple 2</t>
+          <t>Móc 2</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Grapple 4</t>
+          <t>Móc 4</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Triệu hồi Echo tự hủy khi né tránh</t>
+          <t>Triệu hồi Echo tự hủy khi né tránh.</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Nhân Danh Những Anh Hùng</t>
+          <t>Nhân Danh Anh Hùng</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Serenity</t>
+          <t>Bình Yên</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Turmoil</t>
+          <t>Hỗn Loạn</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>The Eternal Watch</t>
+          <t>Người Canh Gác Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Những Linh Hồn Ngoài Hố Đen</t>
+          <t>Những Linh Hồn Vượt Qua Hố Đen</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4845,8 +4845,8 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>"Hãy mang theo khúc ca này—"
-"—Và để lại nụ cười của em cho anh—"</t>
+          <t>"Hãy mang bài hát này theo bên mình—"
+"Và để lại nụ cười ấy cho ta—"</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>Debts Paid In Full</t>
+          <t>Món nợ đã trả đủ</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>High Adjudicator</t>
+          <t>Thẩm Phán Tối Cao</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>The Slumbering Seabed</t>
+          <t>Đại Dương Ngủ Quên</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5126,7 +5126,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>The Somnoire Breeze</t>
+          <t>Gió Somnoire</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Cái Nôi Vĩnh Hằng</t>
+          <t>Nôi Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>The Long Featurette</t>
+          <t>Phim Tài Liệu Dài Tập</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5336,7 +5336,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Ending Locked</t>
+          <t>Kết Thúc Đã Bị Khóa</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5406,7 +5406,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Mở Khóa 1 Kết Thúc</t>
+          <t>Mở khóa 1 Kết Thúc</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Mở Khóa 2 Kết Thúc</t>
+          <t>Mở khóa 2 Kết Thúc</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5546,7 +5546,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Mở Khóa 4 Kết Thúc</t>
+          <t>Mở khóa 4 Kết Thúc</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5616,7 +5616,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Mở Khóa 6 Kết Thúc</t>
+          <t>Mở khóa 6 Kết thúc</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5686,7 +5686,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Mở Khóa 8 Kết Thúc</t>
+          <t>Mở khóa 8 Kết thúc</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Mở Khóa 12 Kết Thúc</t>
+          <t>Mở khóa 12 Kết Cục</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5826,7 +5826,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Clear "Biến Đổiing Hero: Flame Ranger"</t>
+          <t>Hoàn thành "Anh Hùng Biến Hình: Kỵ Sĩ Lửa".</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5896,7 +5896,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Clear "Psyche Pass: The Outlier"</t>
+          <t>Hoàn thành "Psyche Pass: The Outlier".</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6176,7 +6176,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Nhận được tổng cộng 6.000 Giấc Mơ Có Thể Giao Dịch</t>
+          <t>Thu thập tổng cộng 6.000 Giấc Mơ Giao Dịch</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6246,7 +6246,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Nhận được tổng cộng 15.000 Giấc Mơ Có Thể Giao Dịch</t>
+          <t>Tổng cộng thu thập 15.000 Giấc Mơ Có Thể Trao Đổi.</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Complete "Ragunna's Visitor"</t>
+          <t>Hoàn thành "Vị Khách Của Ragunna"</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Complete "The Cinema House Murders"</t>
+          <t>Hoàn thành "Vụ Án Rạp Chiếu Phim".</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6456,7 +6456,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Nhận được tổng cộng 30.000 Giấc Mơ Có Thể Giao Dịch</t>
+          <t>Tổng cộng thu thập 30.000 Giấc Mơ Có Thể Giao Dịch.</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Mở khóa Kết thúc "Vị Khách của Ragunna: Thẩm Phán Tối Cao"</t>
+          <t>Mở khóa Kết Thúc "Vị Khách Của Ragunna: Thẩm Phán Tối Cao"</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6596,7 +6596,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Mở khóa Kết thúc "Vụ Án Rạp Chiếu Phim: Làn Gió Ngủ Mơ"</t>
+          <t>Mở khóa Kết Thúc "Vụ Án Rạp Chiếu Phim: Gió Ngủ Mơ"</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6666,7 +6666,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Nhận Thưởng</t>
+          <t>Nhận thưởng</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6806,7 +6806,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Cooldown Reduction</t>
+          <t>Giảm Thời gian hồi chiêu</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6946,7 +6946,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Dream Residue I</t>
+          <t>Dư Vị Giấc Mơ I</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7016,7 +7016,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Dream Đặt lại I</t>
+          <t>Thiết Lập Lại Giấc Mơ I</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7086,7 +7086,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Damage Increase I</t>
+          <t>Tăng Sát Thương I</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7226,7 +7226,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Awakened Will</t>
+          <t>Ý Chí Thức Tỉnh</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7296,7 +7296,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Damage Increase II</t>
+          <t>Tăng Sát Thương II</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Dream Residue II</t>
+          <t>Dư Vị Giấc Mơ II</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Damage Increase III</t>
+          <t>Tăng Sát Thương III</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Dream Đặt lại II</t>
+          <t>Đặt Lại Giấc Mơ II</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7716,7 +7716,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Dodge Recovery</t>
+          <t>Phục hồi né tránh</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7786,7 +7786,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Quà Tặng Giấc Mơ I</t>
+          <t>Quà tặng Giấc Mơ I</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7856,7 +7856,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Quà Tặng Giấc Mơ II</t>
+          <t>Quà tặng Giấc Mơ II</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7926,7 +7926,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Quà Tặng Giấc Mơ III</t>
+          <t>Mộng Ảo III</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Quà Tặng Giấc Mơ IV</t>
+          <t>Mộng Ảo IV</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8066,7 +8066,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Dream Đặt lại</t>
+          <t>Thiết Lập Lại Giấc Mơ</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8136,7 +8136,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Dreamworld Showdown</t>
+          <t>Đọ Sức Mộng Ảo</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8206,7 +8206,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Accelerated Liberation</t>
+          <t>Giải Phóng Tăng Tốc</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8276,7 +8276,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Cooldown Reduction</t>
+          <t>Giảm Thời gian hồi chiêu</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8346,7 +8346,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>HP Up</t>
+          <t>Tăng HP</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>DMG Reduction</t>
+          <t>Giảm Sát Thương</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8486,7 +8486,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Dodge Recovery</t>
+          <t>Phục hồi né tránh</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8556,7 +8556,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>HP Up</t>
+          <t>Tăng HP</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>DEF Up</t>
+          <t>Tăng Phòng Ngự</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8696,7 +8696,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>DMG Reduction</t>
+          <t>Giảm Sát Thương</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8766,7 +8766,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Dodge Recovery Ⅱ</t>
+          <t>Phục hồi né tránh II</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8836,7 +8836,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Speedy Resonance</t>
+          <t>Cộng Hưởng Tốc Độ</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8906,7 +8906,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Crit. DMG Up</t>
+          <t>Tăng Crit. DMG</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8976,7 +8976,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Accelerated Liberation</t>
+          <t>Giải Phóng Tăng Tốc</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9046,7 +9046,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Crit. DMG Up</t>
+          <t>Tăng Crit. DMG</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>DMG Up</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9186,7 +9186,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Dream Đặt lại I</t>
+          <t>Thiết Lập Lại Giấc Mơ I</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Quà Tặng Giấc Mơ</t>
+          <t>Quà tặng Giấc Mơ</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Cooldown Reduction</t>
+          <t>Giảm Thời gian hồi chiêu</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Dream Residue I</t>
+          <t>Dư Vị Giấc Mơ I</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9466,7 +9466,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Refresh Cửa hàng</t>
+          <t>Làm mới Cửa Hàng</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9606,7 +9606,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>HP Up</t>
+          <t>Tăng HP</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9676,7 +9676,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>ATK Up</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9746,7 +9746,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>ATK Up</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9816,7 +9816,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>ATK Up</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9886,7 +9886,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>ATK Up</t>
+          <t>Tăng ATK</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>DMG Up</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10026,7 +10026,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Crit. Rate Up</t>
+          <t>Tăng Crit. Rate</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Dreamworld Showdown</t>
+          <t>Đọ Sức Mộng Ảo</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10166,7 +10166,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Dream Residue II</t>
+          <t>Dư Vị Giấc Mơ II</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10236,7 +10236,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>DMG Up</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10306,7 +10306,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Dream Đặt lại II</t>
+          <t>Đặt Lại Giấc Mơ II</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10376,7 +10376,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>DMG Up</t>
+          <t>Tăng Sát Thương</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10446,7 +10446,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Crit. DMG Up</t>
+          <t>Tăng Crit. DMG</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10516,7 +10516,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Dream Residue Ⅲ</t>
+          <t>Dư Vị Giấc Mơ III</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10586,7 +10586,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Liên hoan phim Solaris</t>
+          <t>Liên hoan Điện ảnh Solaris</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Featured Trial Resonators</t>
+          <t>Resonator Thử Nghiệm Đặc Sắc</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10726,7 +10726,7 @@
       </c>
       <c r="M147" t="inlineStr">
         <is>
-          <t>Permanent Trial Resonators</t>
+          <t>Resonator Thử nghiệm Vĩnh viễn</t>
         </is>
       </c>
       <c r="N147" t="inlineStr">
@@ -10796,7 +10796,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Trial Resonators</t>
+          <t>Resonator Thử Nghiệm</t>
         </is>
       </c>
       <c r="N148" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>My Resonators</t>
+          <t>Những Resonator của ta...</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10936,7 +10936,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Unavailable Resonators</t>
+          <t>Resonator không khả dụng</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11006,7 +11006,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Nhịp Điệu Của Gió</t>
+          <t>Giai Điệu Gió</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11076,7 +11076,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Hãy Hòa Mình Vào Gió</t>
+          <t>Hiến dâng bản thân cho gió</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11146,7 +11146,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Sống Trong Hơi Thở</t>
+          <t>Sinh Mệnh Trong Hơi Thở</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="M154" t="inlineStr">
         <is>
-          <t>Riding Winds</t>
+          <t>Gió Phiêu Lưu</t>
         </is>
       </c>
       <c r="N154" t="inlineStr">
@@ -11356,7 +11356,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Special Enhancements</t>
+          <t>Các Tăng Cường Đặc Biệt</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11426,7 +11426,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>Unlimited Firepower</t>
+          <t>Hỏa Lực Vô Hạn</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11496,7 +11496,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>Rekindled Spirit</t>
+          <t>Tinh Thần Tái Sinh</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11566,7 +11566,7 @@
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Special Enhancement</t>
+          <t>Tăng Cường Đặc Biệt</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -11636,7 +11636,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Surprise Shot</t>
+          <t>Phát Bắn Bất Ngờ</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11706,7 +11706,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Even More Ferocious</t>
+          <t>Còn Hung Hãn Hơn Nữa</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11776,7 +11776,7 @@
       </c>
       <c r="M162" t="inlineStr">
         <is>
-          <t>Special Enhancement</t>
+          <t>Tăng Cường Đặc Biệt</t>
         </is>
       </c>
       <c r="N162" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Nhiễm Đam Mê</t>
+          <t>Nung Nấu Đam Mê</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11916,7 +11916,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Thunderbolt Ruling</t>
+          <t>Thống Lĩnh Sấm Sét</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11986,7 +11986,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Extraordinary Overload</t>
+          <t>Quá Tải Siêu Phàm</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12056,7 +12056,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Fatal Phantom Pain</t>
+          <t>Ảo Giác Đau Đớn Tử Thần</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Magnetic Current Rush</t>
+          <t>Dòng Từ Đột Kích</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12196,7 +12196,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Electricity Penetration</t>
+          <t>Xuyên Thấu Điện</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12266,7 +12266,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Parry Field</t>
+          <t>Lĩnh vực Né tránh</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Heavy Blade</t>
+          <t>Lưỡi Kiếm Nặng</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12406,7 +12406,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Rocky Protector</t>
+          <t>Người Bảo Vệ Đá Tảng</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12476,7 +12476,7 @@
       </c>
       <c r="M172" t="inlineStr">
         <is>
-          <t>Dual Efficacy</t>
+          <t>Hiệu Quả Kép</t>
         </is>
       </c>
       <c r="N172" t="inlineStr">
@@ -12546,7 +12546,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Threshold Response</t>
+          <t>Phản Ứng Ngưỡng</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12616,7 +12616,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Variable Substitution</t>
+          <t>Thay Thế Biến Số</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12686,7 +12686,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Aggressive Strategy</t>
+          <t>Chiến Thuật Tấn Công</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12756,7 +12756,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Mimicry Deduction</t>
+          <t>Suy Luận Bắt Chước</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12826,7 +12826,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Special Enhancement</t>
+          <t>Tăng Cường Đặc Biệt</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12896,7 +12896,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Fording Rivers</t>
+          <t>Vượt Sông</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12966,7 +12966,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Abyss Treader</t>
+          <t>Kẻ Đi Trong Vực Sâu</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13036,7 +13036,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Trận Chiến Nơi Hoang Dã</t>
+          <t>Chiến đấu ngoài hoang dã</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13106,7 +13106,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>Ceaseless</t>
+          <t>Vô Tận</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13176,7 +13176,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Faultless</t>
+          <t>Hoàn Hảo</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13246,7 +13246,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Blade Returning</t>
+          <t>Kiếm Trở Về</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13316,7 +13316,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Dusty Sound</t>
+          <t>Âm Thanh Đầy Bụi</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13386,7 +13386,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Folding Shadow</t>
+          <t>Bóng Gấp</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13456,7 +13456,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Kiếm Point</t>
+          <t>Mũi Kiếm</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13526,7 +13526,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Heavy Hum</t>
+          <t>Tiếng Vang Trầm</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13596,7 +13596,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Dusty Sound</t>
+          <t>Âm Thanh Đầy Bụi</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13666,7 +13666,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Technique Training I</t>
+          <t>Rèn luyện Kỹ năng I</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13736,7 +13736,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Technique Training II</t>
+          <t>Rèn luyện Kỹ năng II</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13806,7 +13806,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Reverberation</t>
+          <t>Sự Giao Thoa Âm Thanh</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13876,7 +13876,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>The Crownless</t>
+          <t>Vị Vua Không Vương Miện</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Roving Journey</t>
+          <t>Hành Trình Lang Thang</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14016,7 +14016,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Compelling Might</t>
+          <t>Sức Mạnh Quyến Rũ</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14086,7 +14086,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Sheep, Sheep</t>
+          <t>Cừu ơi, Cừu</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14156,7 +14156,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Encounter</t>
+          <t>Chạm trán</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14226,7 +14226,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Spring Echo</t>
+          <t>Tiếng Vọng Mùa Xuân</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Vị Khách Từ Bờ Biển</t>
+          <t>Vị Khách Từ Bờ Vực</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Conductor</t>
+          <t>Nhạc trưởng</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -14506,7 +14506,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>To The Top</t>
+          <t>Đến Đỉnh Cao</t>
         </is>
       </c>
       <c r="N201" t="inlineStr">
@@ -14576,7 +14576,7 @@
       </c>
       <c r="M202" t="inlineStr">
         <is>
-          <t>Lưỡi Kiếm Hủy Diệt</t>
+          <t>Thanh Kiếm Hủy Diệt</t>
         </is>
       </c>
       <c r="N202" t="inlineStr">
@@ -14646,7 +14646,7 @@
       </c>
       <c r="M203" t="inlineStr">
         <is>
-          <t>"Little Thing"</t>
+          <t>"Thằng/Cô Nhóc"</t>
         </is>
       </c>
       <c r="N203" t="inlineStr">
@@ -14716,7 +14716,7 @@
       </c>
       <c r="M204" t="inlineStr">
         <is>
-          <t>Story CG 23</t>
+          <t>CG Câu Chuyện 23</t>
         </is>
       </c>
       <c r="N204" t="inlineStr">
@@ -14786,7 +14786,7 @@
       </c>
       <c r="M205" t="inlineStr">
         <is>
-          <t>Story CG 24</t>
+          <t>CG Câu Chuyện 24</t>
         </is>
       </c>
       <c r="N205" t="inlineStr">
@@ -14856,7 +14856,7 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>Story CG 25</t>
+          <t>CG Câu Chuyện 25</t>
         </is>
       </c>
       <c r="N206" t="inlineStr">
@@ -14926,7 +14926,7 @@
       </c>
       <c r="M207" t="inlineStr">
         <is>
-          <t>Story CG 26</t>
+          <t>CG Câu Chuyện 26</t>
         </is>
       </c>
       <c r="N207" t="inlineStr">
@@ -14996,7 +14996,7 @@
       </c>
       <c r="M208" t="inlineStr">
         <is>
-          <t>Story CG 27</t>
+          <t>CG Câu Chuyện 27</t>
         </is>
       </c>
       <c r="N208" t="inlineStr">
@@ -15066,7 +15066,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Story CG 28</t>
+          <t>CG Câu Chuyện 28</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15136,7 +15136,7 @@
       </c>
       <c r="M210" t="inlineStr">
         <is>
-          <t>Story CG 29</t>
+          <t>CG Câu Chuyện 29</t>
         </is>
       </c>
       <c r="N210" t="inlineStr">
@@ -15206,7 +15206,7 @@
       </c>
       <c r="M211" t="inlineStr">
         <is>
-          <t>Story CG 30</t>
+          <t>CG Câu Chuyện 30</t>
         </is>
       </c>
       <c r="N211" t="inlineStr">
@@ -15276,7 +15276,7 @@
       </c>
       <c r="M212" t="inlineStr">
         <is>
-          <t>Story CG 31</t>
+          <t>CG Câu Chuyện 31</t>
         </is>
       </c>
       <c r="N212" t="inlineStr">
@@ -15346,7 +15346,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Story CG 32</t>
+          <t>CG Câu Chuyện 32</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15416,7 +15416,7 @@
       </c>
       <c r="M214" t="inlineStr">
         <is>
-          <t>Story CG 33</t>
+          <t>CG Câu Chuyện 33</t>
         </is>
       </c>
       <c r="N214" t="inlineStr">
@@ -15486,7 +15486,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Story CG 34</t>
+          <t>CG Câu Chuyện 34</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="M216" t="inlineStr">
         <is>
-          <t>Story CG 35</t>
+          <t>CG Câu Chuyện 35</t>
         </is>
       </c>
       <c r="N216" t="inlineStr">
@@ -15626,7 +15626,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Story CG 36</t>
+          <t>CG Câu Chuyện 36</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15696,7 +15696,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Story CG 37</t>
+          <t>CG Câu Chuyện 37</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15766,7 +15766,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Story CG 38</t>
+          <t>CG Câu Chuyện 38</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15836,7 +15836,7 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>Story CG 39</t>
+          <t>CG Câu Chuyện 39</t>
         </is>
       </c>
       <c r="N220" t="inlineStr">
@@ -15906,7 +15906,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Story CG 40</t>
+          <t>CG Câu Chuyện 40</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15976,7 +15976,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>New Ally</t>
+          <t>Đồng Minh Mới</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16046,7 +16046,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Spring Thunder</t>
+          <t>Sấm Xuân</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16116,7 +16116,7 @@
       </c>
       <c r="M224" t="inlineStr">
         <is>
-          <t>Gặp Gỡ Thần Linh</t>
+          <t>Gặp gỡ Thần Linh</t>
         </is>
       </c>
       <c r="N224" t="inlineStr">
@@ -16186,7 +16186,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Trail Blazer</t>
+          <t>Người Mở Đường</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16326,7 +16326,7 @@
       </c>
       <c r="M227" t="inlineStr">
         <is>
-          <t>Observer's Observer</t>
+          <t>Người Quan Sát Người Quan Sát</t>
         </is>
       </c>
       <c r="N227" t="inlineStr">
@@ -16396,7 +16396,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Stargazer's Dawn</t>
+          <t>Bình Minh Kẻ Ngắm Sao</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16466,7 +16466,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Kết Thúc Lang Thang</t>
+          <t>Chấm dứt Lang thang</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16606,7 +16606,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Qua Mây Đen Và Đá Ngầm Bất Trắc</t>
+          <t>Vượt Qua Mây Đen Và Những Vách Đá Bất Ngờ</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16676,7 +16676,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Bạch Phai Không Cần Ai Thương Tiếc</t>
+          <t>Màu Trắng Phai Mờ Không Cần Ai Thương Xót</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16746,7 +16746,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Như Một Phản Chiếu Trong Con Mắt Thông Thái</t>
+          <t>Như Ảnh Chiếu Trong Con Mắt Thông Thái</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16816,7 +16816,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Bản Ngôn Tự Chào Đón Sự Trở Lại</t>
+          <t>Khúc Ca Ngôn Ngữ Trở Lại</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16886,7 +16886,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>The Night Shines Ever Bright</t>
+          <t>Đêm Rạng Ngời Muôn Thuở</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16956,7 +16956,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Crimson Invitation</t>
+          <t>Lời Mời Đỏ Rực</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17026,7 +17026,7 @@
       </c>
       <c r="M237" t="inlineStr">
         <is>
-          <t>Dàn Hợp Xướng Im Lặng Dâng Tặng Nhân Danh Một Vở Kịch</t>
+          <t>Vở Diễn Vô Thanh Dâng Tặng Nhân Danh Một Vở Kịch</t>
         </is>
       </c>
       <c r="N237" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Tacit Steps</t>
+          <t>Bước Đi Vô Tiếng</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17166,7 +17166,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Bay, Bay Lên Trời Cao</t>
+          <t>Bay đi, bay lên trời cao</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17236,7 +17236,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Khúc Ru Cuối Cùng Của Đêm</t>
+          <t>Khúc Ru Đêm Cuối Cùng</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17446,7 +17446,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>The Ending Cô ấy Desired</t>
+          <t>Kết Cục Nàng Mong Muốn</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17516,7 +17516,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Slaying the Evil</t>
+          <t>Diệt Ác</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17586,7 +17586,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Fulfilled Expectation</t>
+          <t>Đáp Ứng Kỳ Vọng</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17656,7 +17656,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>A Moment to Remember</t>
+          <t>Khoảnh Khắc Đáng Nhớ</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>When Music First Sounded</t>
+          <t>Khi Âm Nhạc Cất Lên Lần Đầu</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17796,7 +17796,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Mùa Hè Của Bạn Sẽ Không Tàn Phai</t>
+          <t>Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17866,7 +17866,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>A Wolfy Greeting</t>
+          <t>Lời Chào Của Sói Con</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17936,7 +17936,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Together</t>
+          <t>Cùng Nhau</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18006,7 +18006,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>The Last Arena</t>
+          <t>Đấu Trường Cuối Cùng</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Reunion</t>
+          <t>Đoàn tụ</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18146,7 +18146,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Cuối Cùng Cũng Daybreak</t>
+          <t>Cuối Cùng Cũng Bình Minh</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18216,7 +18216,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Trở về của Trái Tim Hoang Dã</t>
+          <t>Trở Về Của Trái Tim Hoang Dã</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Con Đường Cô Đơn</t>
+          <t>Con Đường Cô Độc</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18356,7 +18356,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Lửa Bất Tử</t>
+          <t>Lửa Bất Diệt</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18426,7 +18426,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Story CG 1005</t>
+          <t>CG Câu Chuyện 1005</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18496,7 +18496,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Story CG 1006</t>
+          <t>CG Câu Chuyện 1006</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18566,7 +18566,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Bản Chất Thật</t>
+          <t>Bản Lĩnh Thật</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18636,7 +18636,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Wooly Nhỏ, Cuộc Phiêu Lưu Lớn</t>
+          <t>Cừu Nhỏ, Đại Phiêu Lưu</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18706,7 +18706,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Nở Hoa Trong Mưa</t>
+          <t>Hoa Nở Trong Mưa</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18846,7 +18846,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Đêm Đắng Cay Không Ngủ</t>
+          <t>Đêm Đắng Không Giấc Ngủ</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18916,7 +18916,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Đêm Ngập Sao</t>
+          <t>Đêm Ngàn Sao</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18986,7 +18986,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Midnight Improv</t>
+          <t>Biểu Diễn Ngẫu Hứng Nửa Đêm</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19056,7 +19056,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Giấc Mơ Đêm Thoáng Qua</t>
+          <t>Giấc Mộng Đêm Thoáng Qua</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19126,7 +19126,7 @@
       </c>
       <c r="M267" t="inlineStr">
         <is>
-          <t>As Dawn Breaks</t>
+          <t>Khi Bình Minh Ló Rạng</t>
         </is>
       </c>
       <c r="N267" t="inlineStr">
@@ -19196,7 +19196,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>The Final Debt</t>
+          <t>Nợ Cuối Cùng</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19266,7 +19266,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Lời Chúc Phúc Dành Cho Những Vì Sao Sắp Lặn</t>
+          <t>Lời Chúc Phúc Cho Những Vì Sao Sắp Tắt</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Cuộc Chạm Trán Định Mệnh Với Kẻ Thù Không Đội Trời Chung</t>
+          <t>Cuộc Đụng Độ Định Mệnh Với Kẻ Thù Không Đội Trời Chung</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19406,7 +19406,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Cheers To The Soldiers</t>
+          <t>Hoan hô các chiến binh!</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19476,7 +19476,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Bí Mật Giữa Anh Và Em</t>
+          <t>Bí Mật Chỉ Riêng Ta Biết</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19546,7 +19546,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Ngôn Ngữ Câm Lặng và Chân Thành Của Cây Cỏ</t>
+          <t>Im Lặng &amp; Chân Thành Là Ngôn Ngữ Của Cây Cỏ</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19616,7 +19616,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Ooh, Here Bạn Are</t>
+          <t>Ôi, bạn đây rồi!</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19686,7 +19686,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Chant The Elegy</t>
+          <t>Hát Khúc Bi Ca</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19756,7 +19756,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Nhanh Lên Đến Tổ Tai Họa</t>
+          <t>Nhanh lên, đến Tổ Tai Họa ngay!</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19826,7 +19826,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Bóng Tối Cổ Xưa Gầm Thét Trên Bầu Trời Tấn Châu</t>
+          <t>Âm Thanh Cổ Xưa Gào Thét Trên Bầu Trời Cẩm Châu</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -19896,7 +19896,7 @@
       </c>
       <c r="M278" t="inlineStr">
         <is>
-          <t>Stomach Full</t>
+          <t>No bụng rồi</t>
         </is>
       </c>
       <c r="N278" t="inlineStr">
@@ -19966,7 +19966,7 @@
       </c>
       <c r="M279" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 23</t>
+          <t>Mô tả CG Câu Chuyện 23</t>
         </is>
       </c>
       <c r="N279" t="inlineStr">
@@ -20036,7 +20036,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 24</t>
+          <t>Mô tả CG Câu Chuyện 24</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20106,7 +20106,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 25</t>
+          <t>Mô tả CG Câu Chuyện 25</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20176,7 +20176,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 26</t>
+          <t>Mô tả CG Câu Chuyện 26</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20246,7 +20246,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 27</t>
+          <t>Cảnh CG Truyện 27</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20316,7 +20316,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 28</t>
+          <t>Cảnh CG Truyện 28</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20386,7 +20386,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Story CG Mô tả 29</t>
+          <t>Cảnh CG Truyện 29</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20456,7 +20456,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 30</t>
+          <t>Cảnh CG Truyện 30</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20526,7 +20526,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 31</t>
+          <t>Cảnh CG Truyện 31</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20596,7 +20596,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 32</t>
+          <t>Cảnh CG Truyện 32</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20666,7 +20666,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 33</t>
+          <t>Cảnh CG Truyện 33</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20736,7 +20736,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 34</t>
+          <t>Cảnh CG Truyện 34</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20806,7 +20806,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 35</t>
+          <t>Cảnh CG Truyện 35</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20876,7 +20876,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 36</t>
+          <t>Cảnh CG Truyện 36</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20946,7 +20946,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 37</t>
+          <t>Cảnh CG Truyện 37</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21016,7 +21016,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 38</t>
+          <t>Cảnh CG Truyện 38</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21086,7 +21086,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 39</t>
+          <t>Mô tả CG Cốt Truyện 39</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 40</t>
+          <t>Mô tả CG Cốt Truyện 40</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21226,7 +21226,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Ôm Trọn Quá Khứ Với Bước Chân Kiên Định</t>
+          <t>Ôm Trọn Quá Khứ Bằng Bước Chân Kiên Định</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21296,7 +21296,7 @@
       </c>
       <c r="M298" t="inlineStr">
         <is>
-          <t>Tiếng Chuông Trong Vang Tẩy Uế Hung Tà</t>
+          <t>Tiếng Chuông Trong Trắng Thanh Tẩy Tà Ác</t>
         </is>
       </c>
       <c r="N298" t="inlineStr">
@@ -21366,7 +21366,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Curtains Up, Thunder Strikes</t>
+          <t>Bắt Đầu, Tia Sét Giáng Trần</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21436,7 +21436,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 1005</t>
+          <t>Mô tả CG Câu Chuyện 1005</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21506,7 +21506,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Mô tả CG Câu chuyện 1006</t>
+          <t>Mô tả CG Câu Chuyện 1006</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21576,7 +21576,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Lời Mở Đầu: Âm Thanh Kỳ Diệu</t>
+          <t>Khúc dạo đầu: Lời Tán Tụng Kỳ Diệu</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21646,7 +21646,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Dư Âm Hành Quân</t>
+          <t>Huanglong - Chương I: Echoing Marche</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21716,7 +21716,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Ngôi Sao Điềm Báo</t>
+          <t>Huanglong - Chương I: Ngôi Sao Điềm Gở</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21786,7 +21786,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Kiếm Kích Bên Nhau</t>
+          <t>Huanglong - Chương I: Lưỡi Kiếm Va Chạm</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="M306" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Giọt Mưa Quay Ngược Thời Gian</t>
+          <t>Huanglong - Chương I: Giọt Mưa Lùi Thời Gian</t>
         </is>
       </c>
       <c r="N306" t="inlineStr">
@@ -21926,7 +21926,7 @@
       </c>
       <c r="M307" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Cơn Bão Chiến Tranh Vĩ Đại</t>
+          <t>Huanglong - Chương I: Đại Chiến Bão</t>
         </is>
       </c>
       <c r="N307" t="inlineStr">
@@ -21996,7 +21996,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Người Bạn Đồng Hành Mới</t>
+          <t>Huanglong - Chương I: Người Bạn Mới</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22066,7 +22066,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Huanglong - Chương I: Sự Tan Băng Của Thời Gian</t>
+          <t>Huanglong - Chương I: Băng Tan Muôn Thuở</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22136,7 +22136,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Black Shores - Chương I: Đến Tận Cùng Bờ Biển</t>
+          <t>Bờ Biển Đen - Chương I: Đến Tận Cùng Bờ Biển</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22206,7 +22206,7 @@
       </c>
       <c r="M311" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Sự Kiện: Khi Đêm Gõ Cửa</t>
+          <t>Sự Kiện: Khi Đêm Gõ Cửa</t>
         </is>
       </c>
       <c r="N311" t="inlineStr">
@@ -22276,7 +22276,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Chương II Rinascita: Vượt Biển Khơi</t>
+          <t>Chương II Rinascita: Vượt Qua Đại Dương, Ngươi Sẽ Đột Phá</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22346,7 +22346,7 @@
       </c>
       <c r="M313" t="inlineStr">
         <is>
-          <t>Chương II Rinascita: Luồng Gió Thiêng Thường Xuyên Thổi</t>
+          <t>Chương II Rinascita: Luồng Gió Thiêng Thường Xuyên Thổi Qua</t>
         </is>
       </c>
       <c r="N313" t="inlineStr">
@@ -22416,7 +22416,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Chương II Rinascita: Bỏ Màn Trong Nắng Hay Bóng Tối</t>
+          <t>Chương II Rinascita: Bức Màn Bị Kéo Lên Dù Trong Ánh Sáng Hay Bóng Tối</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22486,7 +22486,7 @@
       </c>
       <c r="M315" t="inlineStr">
         <is>
-          <t>Chương II Rinascita: Điều Hôm Qua Khóc, Hôm Nay Sẽ Hát</t>
+          <t>Chương II Rinascita: Điều Hôm Qua Khóc Than, Hôm Nay Sẽ Cất Lên Tiếng Hát</t>
         </is>
       </c>
       <c r="N315" t="inlineStr">
@@ -22556,7 +22556,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>Chương II Rinascita: Thiếu Nữ, Kẻ Thách Thức, Kẻ Rao Tin Chết Chóc</t>
+          <t>Chương II Rinascita: Thiếu Nữ, Kẻ Nổi Loạn, Người Rao Tin Tử Thần</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22626,7 +22626,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Sự Kiện "Cube, Cubic n Cubie"</t>
+          <t>Nhiệm vụ sự kiện "Cube, Cubic và Cubie"</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22696,7 +22696,7 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ Sự Kiện "Mùa Hè Của Bạn Sẽ Không Bao Giờ Tàn Úa"</t>
+          <t>Sự Kiện "Mùa Hè Của Ngươi Sẽ Không Bao Giờ Tàn Úa"</t>
         </is>
       </c>
       <c r="N318" t="inlineStr">
@@ -22836,7 +22836,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Chương II Rinascita: Ngọn Lửa Trong Tim</t>
+          <t>Chương II: Rinascita - Ngọn Lửa Trong Tim</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22976,7 +22976,7 @@
       </c>
       <c r="M322" t="inlineStr">
         <is>
-          <t>Companion Story: Wild Heart's Return</t>
+          <t>Truyện Đồng Hành: Trở Về Của Trái Tim Hoang Dã</t>
         </is>
       </c>
       <c r="N322" t="inlineStr">
@@ -23046,7 +23046,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Companion Story: Solitary Path</t>
+          <t>Truyện Đồng Hành: Con Đường Cô Đơn</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23116,7 +23116,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Companion Story: Immortal Blaze</t>
+          <t>Truyện Đồng Hành: Ngọn Lửa Bất Tử</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23186,7 +23186,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Companion Story: True Colors</t>
+          <t>Truyện Đồng Hành: Bản Chất Thật Sự</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23256,7 +23256,7 @@
       </c>
       <c r="M326" t="inlineStr">
         <is>
-          <t>Câu Chuyện Đồng Hành: Cừu Nhỏ, Những Chuyến Phiêu Lưu Lớn</t>
+          <t>Truyện Đồng Hành: Cừu Nhỏ, Đại Mạo Hiểm</t>
         </is>
       </c>
       <c r="N326" t="inlineStr">
@@ -23326,7 +23326,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Câu Chuyện Đồng Hành: Những Ngã Rẽ Giữa Các Vì Sao</t>
+          <t>Câu Chuyện Đồng Hành: Ngã Ba Giữa Các Vì Sao</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23396,7 +23396,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Câu Chuyện Đồng Hành: Nếu Một Đêm Mưa Có Một Gia Đình</t>
+          <t>Câu Chuyện Đồng Hành: Nếu Một Đêm Mưa Có Gia Đình</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23466,7 +23466,7 @@
       </c>
       <c r="M329" t="inlineStr">
         <is>
-          <t>Câu Chuyện Đồng Hành: Đêm Ngập Sao</t>
+          <t>Truyện Đồng Hành: Đêm Ngập Sao</t>
         </is>
       </c>
       <c r="N329" t="inlineStr">
@@ -23536,7 +23536,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Câu Chuyện Đồng Hành: Giấc Mơ Đêm Ngắn Ngủi</t>
+          <t>Câu Chuyện Đồng Hành: Giấc Mộng Đêm Ngắn Ngủi</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23606,7 +23606,7 @@
       </c>
       <c r="M331" t="inlineStr">
         <is>
-          <t>Câu Chuyện Đồng Hành "Ngọn Lửa Trong Bóng Tối"</t>
+          <t>Câu Chuyện Đồng Hành "Ánh Lửa Trong Bóng Tối"</t>
         </is>
       </c>
       <c r="N331" t="inlineStr">
@@ -23676,7 +23676,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Sẵn Sàng và Tập Hợp</t>
+          <t>Sẵn sàng và tập trung</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23746,7 +23746,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Heavy Work</t>
+          <t>Công Việc Nặng Nhọc</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23816,7 +23816,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Tấn Công Trong Khi Phòng Thủ</t>
+          <t>Tấn công trong trạng thái Phòng Ngự</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -24026,7 +24026,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Zhao Shuang</t>
+          <t>Triệu Sương</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24516,7 +24516,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Yi KouJing</t>
+          <t>Nhất Khẩu Tinh</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24586,7 +24586,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Liang DaWei</t>
+          <t>Lương Đại Vĩ</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24656,7 +24656,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Sun Ye</t>
+          <t>Tôn Dã</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24796,7 +24796,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Xu Xiang</t>
+          <t>Hứ Hương</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -25006,7 +25006,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Lucky Fish</t>
+          <t>Cá May Mắn</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -26616,7 +26616,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Chase Brown</t>
+          <t>Truy đuổi Brown</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -27106,7 +27106,7 @@
       </c>
       <c r="M381" t="inlineStr">
         <is>
-          <t>James Ngày</t>
+          <t>James Day</t>
         </is>
       </c>
       <c r="N381" t="inlineStr">
@@ -27946,7 +27946,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Yu Yeong</t>
+          <t>Dư Anh</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28016,7 +28016,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Yi Sae Ah</t>
+          <t>Nhất Sa Á</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28926,7 +28926,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Highland Dreams</t>
+          <t>Giấc Mơ Cao Nguyên</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28996,7 +28996,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>COST 4 Enhanced Drop Rate</t>
+          <t>CHI PHÍ 4 Tăng Tỷ Lệ Rơi Đồ</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Tăng Tỉ Lệ Rơi Đồ Nâng Cấp Cost 1 &amp; Cost 3</t>
+          <t>Tỷ Lệ Rơi Tăng Cường Chi Phí 1 &amp; Chi Phí 3</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29136,7 +29136,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Common | Elite</t>
+          <t>Thường gặp | Cao cấp</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29206,7 +29206,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>1-Star</t>
+          <t>1 Sao</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29276,7 +29276,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>2-Star</t>
+          <t>2 Sao</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29346,7 +29346,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>3-Star</t>
+          <t>3 Sao</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29416,7 +29416,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>4-Star</t>
+          <t>4 Sao</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29486,7 +29486,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>5-Star</t>
+          <t>5 Sao</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29556,7 +29556,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Rapid Grapple</t>
+          <t>Túm Nhanh</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29626,7 +29626,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Investigation Terminated</t>
+          <t>Điều tra Đã Kết Thúc</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Đã bán hết</t>
+          <t>Hết hàng</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -30046,7 +30046,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Monster Points</t>
+          <t>Điểm quái vật</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30116,7 +30116,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Time Points</t>
+          <t>Điểm Thời Gian</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30186,7 +30186,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Technical Points</t>
+          <t>Điểm Kỹ Thuật</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30326,7 +30326,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30396,7 +30396,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Suggested Attribute</t>
+          <t>Thuộc tính đề xuất</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30466,7 +30466,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Suggested Attribute: N/A</t>
+          <t>Thuộc tính đề xuất: Không</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30606,7 +30606,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Đội Limit Reached</t>
+          <t>Đã Đạt Giới Hạn Đội</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30676,7 +30676,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Your Resonators</t>
+          <t>Resonator của ngươi</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30746,7 +30746,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Trial Resonators</t>
+          <t>Resonator Thử Nghiệm</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30886,7 +30886,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30956,7 +30956,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Coming Soon</t>
+          <t>Sắp ra mắt</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31026,7 +31026,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Vùng Tiếp Theo Sắp Ra Mắt</t>
+          <t>Khu Vực Tiếp Theo Sắp Ra Mắt</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31096,7 +31096,7 @@
       </c>
       <c r="M438" t="inlineStr">
         <is>
-          <t>Hỗ Trợ và Chữa Trị</t>
+          <t>Hỗ trợ và Hồi phục</t>
         </is>
       </c>
       <c r="N438" t="inlineStr">
@@ -31166,7 +31166,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Traction</t>
+          <t>Lực kéo</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31236,7 +31236,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Coordinated Attack</t>
+          <t>Tấn công phối hợp</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31306,7 +31306,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Stagnation</t>
+          <t>Sự Trì Trệ</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31376,7 +31376,7 @@
       </c>
       <c r="M442" t="inlineStr">
         <is>
-          <t>Vibration Strength Reduction</t>
+          <t>Giảm Cường Độ Rung Động</t>
         </is>
       </c>
       <c r="N442" t="inlineStr">
@@ -31516,7 +31516,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Interruption Resistance Boost</t>
+          <t>Tăng Kháng Ngắt Đòn</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31656,7 +31656,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Điểm Tiêu Diệt Quái Vật:</t>
+          <t>Điểm tiêu diệt quái:</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31726,7 +31726,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Điểm Thời Gian Còn Lại:</t>
+          <t>Điểm thời gian còn lại:</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31866,7 +31866,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31936,7 +31936,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Proceed</t>
+          <t>Tiến lên</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32006,7 +32006,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>First Impression</t>
+          <t>Ấn Tượng Đầu Tiên</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32076,7 +32076,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>Snowy Trails</t>
+          <t>Những Lối Tuyết</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32146,7 +32146,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Chamber Tides</t>
+          <t>Triều Sóng Trong Hang</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32216,7 +32216,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Sau Cơn Tuyết</t>
+          <t>Sau Tuyết Rơi</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32286,7 +32286,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Hành Trình Đến Firmament"</t>
+          <t>Đạt Cấp Độ Liên Minh 14 và hoàn thành Nhiệm Vụ Chính "Hành Trình Đến Bầu Trời"</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32356,7 +32356,7 @@
       </c>
       <c r="M456" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính: Voyage to Firmament</t>
+          <t>Hoàn thành Nhiệm vụ Chính: Hành Trình Đến Bầu Trời Cố Định.</t>
         </is>
       </c>
       <c r="N456" t="inlineStr">
@@ -32426,7 +32426,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính: Truthseeker's Pass</t>
+          <t>Hoàn thành Nhiệm Vụ Chính: Con Đường Của Kẻ Tìm Sự Thật</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm Vụ Chính: When the Snow Clears</t>
+          <t>Hoàn thành Nhiệm vụ Chính: Khi Tuyết Tan.</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32566,7 +32566,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Thư Giãn Tại Suối Sagaci</t>
+          <t>Hãy đắm mình trong làn nước Sagaci Springs</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32636,7 +32636,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Thu Thập 5 Quả Pavo</t>
+          <t>Thu thập 5 Quả Lý Pavo</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32706,7 +32706,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Echo: Clang Bang tại Hongzhen</t>
+          <t>Hoàn thành Thử Thách Echo: Clang Bang at Hongzhen</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32776,7 +32776,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Stone Lift tại Luminous Shore</t>
+          <t>Hoàn thành thử thách Nâng Đá tại Bãi Biển Lấp Lánh</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32846,7 +32846,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Mở cổng vào tàn tích tại Truthseeker's Pass</t>
+          <t>Mở cổng dẫn đến tàn tích ở Đèo Truthseeker</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -32916,7 +32916,7 @@
       </c>
       <c r="M464" t="inlineStr">
         <is>
-          <t>Thu Thập 5 Ngọc Trai Loong</t>
+          <t>Thu thập 5 Viên Châu Long</t>
         </is>
       </c>
       <c r="N464" t="inlineStr">
@@ -32986,7 +32986,7 @@
       </c>
       <c r="M465" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Echo: Clang Bang tại Xuanji Ridges</t>
+          <t>Hoàn thành Thử Thách Echo: Clang Bang at Xuanji Ridges</t>
         </is>
       </c>
       <c r="N465" t="inlineStr">
@@ -33126,7 +33126,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Kích hoạt Nexus Tower tại Hongzhen</t>
+          <t>Kích hoạt Tháp Nexus tại Hồng Chân</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33266,7 +33266,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Thu Thập 5 Đá Fluorite</t>
+          <t>Thu thập 5 Viên Huỳnh Thạch</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33336,7 +33336,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Echo: Clang Bang tại Loong's Ridge</t>
+          <t>Hoàn thành Thử Thách Echo: Clang Bang at Loong's Ridge</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33406,7 +33406,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Stone Lift tại Tianqu Tree</t>
+          <t>Hoàn thành thử thách Nâng Đá tại Cây Thiên Cự</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33546,7 +33546,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Đạt cấp độ 4 trong Whindchimer Delivery</t>
+          <t>Hoàn thành Cấp 4 Nhiệm Vụ Giao Hàng Whindchimer</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33616,7 +33616,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Hoàn thành Thử Thách Echo: Clang Bang tại Loong's Crest</t>
+          <t>Hoàn thành Thử Thách Echo: Clang Bang at Loong's Crest</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33686,7 +33686,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Đánh bại Lightcrusher bên trong Photon Barrier tại Loong's Ridge</t>
+          <t>Đánh bại Lightcrusher bên trong Rào Photon tại Loong's Ridge</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33756,7 +33756,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Phá bỏ phong ấn ở tàn tích ven biển tại Loong's Crest</t>
+          <t>Phá bỏ phong ấn tại tàn tích ven biển ở Loong's Crest</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33826,7 +33826,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Đánh bại Construct - Protective Scales</t>
+          <t>Tiêu diệt Construct - Vảy Bảo Hộ</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33896,7 +33896,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Moon-Chasing Festival</t>
+          <t>Lễ Hội Đuổi Trăng</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33966,7 +33966,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Border Patrols</t>
+          <t>Các Đội Tuần Tra Biên Giới</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34036,7 +34036,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Route Planning</t>
+          <t>Lập Kế Hoạch Tuyến Đường</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34106,7 +34106,7 @@
       </c>
       <c r="M481" t="inlineStr">
         <is>
-          <t>Self-defense Training</t>
+          <t>Huấn Luyện Tự Vệ</t>
         </is>
       </c>
       <c r="N481" t="inlineStr">
@@ -34176,7 +34176,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Hương vị quá khứ</t>
+          <t>Hương Vị Xưa</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34246,7 +34246,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Ingredient Collection</t>
+          <t>Thu thập Nguyên liệu</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34316,7 +34316,7 @@
       </c>
       <c r="M484" t="inlineStr">
         <is>
-          <t>Chef's Masterclass</t>
+          <t>Bài Giảng Thực Tế Của Đầu Bếp</t>
         </is>
       </c>
       <c r="N484" t="inlineStr">
@@ -34386,7 +34386,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Huyền thoại Hollow Tree</t>
+          <t>Huyền Thoại Hốc Cây</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34456,7 +34456,7 @@
       </c>
       <c r="M486" t="inlineStr">
         <is>
-          <t>Ghostwriter Needed</t>
+          <t>Cần Người Viết Lách Bí Ẩn</t>
         </is>
       </c>
       <c r="N486" t="inlineStr">
@@ -34526,7 +34526,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Nguồn cảm hứng cho câu đố</t>
+          <t>Ý tưởng giải câu đố</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34596,7 +34596,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Casting Jinzhou's Hero</t>
+          <t>Kích hoạt Anh Hùng Jinzhou</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34666,7 +34666,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Echo Show</t>
+          <t>Hiển Thị Âm Hưởng</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34736,7 +34736,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Firework Artistry</t>
+          <t>Nghệ thuật pháo hoa</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34876,7 +34876,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Bộ sưu tập các pha trăng</t>
+          <t>Bảo Tàng Pha Mặt Trăng</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34946,7 +34946,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Express Courier</t>
+          <t>Đại Lý Vận Chuyển Nhanh</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35016,7 +35016,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Festival Guides</t>
+          <t>Hướng Dẫn Lễ Hội</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35086,7 +35086,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Moon-Chasing Photography</t>
+          <t>Chụp Ảnh Đuổi Trăng</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35156,7 +35156,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Jinzhou Revisited</t>
+          <t>Jinzhou Quay Lại</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
